--- a/Config/Excel/Skill@技能配置/BuffStatusTypeConfig@Buff状态类型配置@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/BuffStatusTypeConfig@Buff状态类型配置@cs.xlsx
@@ -38,16 +38,17 @@
     <t>是否叠加层数</t>
   </si>
   <si>
-    <t>如果能够叠加
-最大叠加层数</t>
-  </si>
-  <si>
-    <t>叠加时间方式
+    <t>如果不叠加层数 
+叠加时间方式
 0=最大叠加时间
 1=最小叠加时间
 2=叠加时间之和</t>
   </si>
   <si>
+    <t>如果能够叠加
+最大叠加层数</t>
+  </si>
+  <si>
     <t>可变Json参数</t>
   </si>
   <si>
@@ -60,10 +61,10 @@
     <t>IsBuffStackCount</t>
   </si>
   <si>
+    <t>BuffStatusTimeAddType</t>
+  </si>
+  <si>
     <t>BuffStatusStatckMaxCount</t>
-  </si>
-  <si>
-    <t>BuffStatusTimeAddType</t>
   </si>
   <si>
     <t>BuffStatusParam</t>
@@ -1036,15 +1037,15 @@
     <col min="4" max="4" width="21.625" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="25.75" customWidth="1"/>
-    <col min="7" max="7" width="27.125" customWidth="1"/>
-    <col min="8" max="8" width="26.625" customWidth="1"/>
+    <col min="7" max="7" width="26.625" customWidth="1"/>
+    <col min="8" max="8" width="27.125" customWidth="1"/>
     <col min="9" max="9" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:9">
       <c r="E2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="54" spans="3:9">
+    <row r="3" s="1" customFormat="1" ht="67.5" spans="3:9">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1123,10 +1124,10 @@
       <c r="F6" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1135,98 +1136,112 @@
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="G7"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="3:9">
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="G8"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="3:9">
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="G9"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="3:9">
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="G10"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="3:9">
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="G11"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="3:9">
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="G12"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="3:9">
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="G13"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="3:9">
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="G14"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="3:9">
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="G15"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="3:9">
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="3:7">
+      <c r="G16"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="3:8">
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="3:7">
+      <c r="G17"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="3:8">
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="3:7">
+      <c r="G18"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="3:8">
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="3:7">
+      <c r="G19"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="3:8">
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="G20"/>
+      <c r="H20" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
